--- a/artfynd/A 42487-2024 artfynd.xlsx
+++ b/artfynd/A 42487-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75259043</v>
+        <v>75259041</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6431</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tingsryd, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493148.8002584948</v>
+        <v>492968</v>
       </c>
       <c r="R2" t="n">
-        <v>6250198.251521477</v>
+        <v>6250417</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +743,9 @@
           <t>2018-11-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-11-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +757,16 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Skogsalm, jätteträd</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -789,6 +779,223 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Artinventering för Lst G</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>75259043</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>493149</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6250198</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tingsås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2018-11-12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2018-11-12</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Artinventering för Lst G</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>75259042</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>492969</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6250414</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tingsås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-11-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-11-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Jätteträd</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Artinventering för Lst G</t>
         </is>

--- a/artfynd/A 42487-2024 artfynd.xlsx
+++ b/artfynd/A 42487-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Artinventering för Lst G</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75259041</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
           <t>Artinventering för Lst G</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75259043</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,8 +1015,18 @@
           <t>Artinventering för Lst G</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75259042</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>